--- a/docs/equipment.xlsx
+++ b/docs/equipment.xlsx
@@ -7052,7 +7052,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>dmg_reduce</t>
+          <t>final_dmg_reduce</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -14392,7 +14392,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Thần cung Huyết Ẩn — 80% Chảy Máu on-hit, 5% HP chân thương, mỗi tầng nặng hơn.</t>
+          <t>Thần cung Huyết Ẩn — 80% Chảy Máu on-hit, +5% Sát Thương Chuẩn, mỗi tầng nặng hơn.</t>
         </is>
       </c>
     </row>
@@ -14430,7 +14430,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Trường thương 2H — 80% Chảy Máu on-hit, +3 tầng, 4% HP chân thương.</t>
+          <t>Trường thương 2H — 80% Chảy Máu on-hit, +3 tầng, +4% Sát Thương Chuẩn.</t>
         </is>
       </c>
     </row>
@@ -14506,7 +14506,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Quan Huyết Đạo — +5 tầng, mỗi tầng +0.8% ST, 42% heal-reduce, 5% HP chân thương.</t>
+          <t>Quan Huyết Đạo — +5 tầng, mỗi tầng +0.8% ST, 42% heal-reduce, +5% Sát Thương Chuẩn.</t>
         </is>
       </c>
     </row>
@@ -14582,7 +14582,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Tổ kiếm Huyết Cổ — báu vật thượng cổ, khiến Chảy Máu ngươi gây ra đánh theo **% HP tối đa** mục tiêu (cơ chế cổ rất hiếm). Mọi đòn đánh đều Chảy Máu, 6% HP chân thương.</t>
+          <t>Tổ kiếm Huyết Cổ — báu vật thượng cổ, khiến Chảy Máu ngươi gây ra đánh theo **% HP tối đa** mục tiêu (cơ chế cổ rất hiếm). Mọi đòn đánh đều Chảy Máu, +6% Sát Thương Chuẩn.</t>
         </is>
       </c>
     </row>
@@ -14620,7 +14620,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Tổ kiếm Kim Đạo — mọi đòn gây Chảy Máu, +5 tầng (max 10), 8% HP chân thương.</t>
+          <t>Tổ kiếm Kim Đạo — mọi đòn gây Chảy Máu, +5 tầng (max 10), +8% Sát Thương Chuẩn.</t>
         </is>
       </c>
     </row>
@@ -17432,7 +17432,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Găng Thiên Hà — +4 tầng/đòn, xuyên 25% Kháng Thủy, 4% HP chân thương. Bộ Thiên Hà 3 mảnh.</t>
+          <t>Găng Thiên Hà — +4 tầng/đòn, xuyên 25% Kháng Thủy, +4% Sát Thương Chuẩn. Bộ Thiên Hà 3 mảnh.</t>
         </is>
       </c>
     </row>
